--- a/data/16S/metadata_16S.xlsx
+++ b/data/16S/metadata_16S.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\Documents\GitHub\Augmentum_eDNA_metabarcoding\data\16S\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E496A94C-AA23-4C5C-8159-2C69914A3A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{303B24F4-F08B-4F6E-9779-C605CC0F06A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-9525" windowWidth="29040" windowHeight="15720" xr2:uid="{A98CF8EC-D2DA-4B38-910A-EF3A2677D223}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A98CF8EC-D2DA-4B38-910A-EF3A2677D223}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="123">
   <si>
     <t>01_St1_D1</t>
   </si>
@@ -424,9 +424,6 @@
   </si>
   <si>
     <t>Iterdalk</t>
-  </si>
-  <si>
-    <t>Ocean</t>
   </si>
   <si>
     <t>Tunulliarfik</t>
@@ -1448,7 +1445,7 @@
         <v>89</v>
       </c>
       <c r="I20" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
@@ -1480,7 +1477,7 @@
         <v>89</v>
       </c>
       <c r="I21" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
@@ -1512,7 +1509,7 @@
         <v>89</v>
       </c>
       <c r="I22" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
@@ -1544,7 +1541,7 @@
         <v>91</v>
       </c>
       <c r="I23" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
@@ -1576,7 +1573,7 @@
         <v>91</v>
       </c>
       <c r="I24" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
@@ -1608,7 +1605,7 @@
         <v>91</v>
       </c>
       <c r="I25" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
@@ -2152,7 +2149,7 @@
         <v>105</v>
       </c>
       <c r="I42" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
@@ -2184,7 +2181,7 @@
         <v>105</v>
       </c>
       <c r="I43" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
@@ -2216,7 +2213,7 @@
         <v>105</v>
       </c>
       <c r="I44" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
@@ -2248,7 +2245,7 @@
         <v>107</v>
       </c>
       <c r="I45" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
@@ -2280,7 +2277,7 @@
         <v>107</v>
       </c>
       <c r="I46" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
@@ -2312,7 +2309,7 @@
         <v>107</v>
       </c>
       <c r="I47" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
@@ -2344,7 +2341,7 @@
         <v>109</v>
       </c>
       <c r="I48" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
@@ -2376,7 +2373,7 @@
         <v>109</v>
       </c>
       <c r="I49" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
@@ -2408,7 +2405,7 @@
         <v>109</v>
       </c>
       <c r="I50" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
@@ -2440,7 +2437,7 @@
         <v>111</v>
       </c>
       <c r="I51" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
@@ -2472,7 +2469,7 @@
         <v>111</v>
       </c>
       <c r="I52" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
@@ -2504,7 +2501,7 @@
         <v>111</v>
       </c>
       <c r="I53" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
@@ -2536,7 +2533,7 @@
         <v>113</v>
       </c>
       <c r="I54" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
@@ -2568,7 +2565,7 @@
         <v>113</v>
       </c>
       <c r="I55" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
@@ -2600,7 +2597,7 @@
         <v>113</v>
       </c>
       <c r="I56" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
@@ -2632,7 +2629,7 @@
         <v>115</v>
       </c>
       <c r="I57" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
@@ -2664,7 +2661,7 @@
         <v>115</v>
       </c>
       <c r="I58" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
@@ -2696,7 +2693,7 @@
         <v>115</v>
       </c>
       <c r="I59" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
@@ -2728,7 +2725,7 @@
         <v>117</v>
       </c>
       <c r="I60" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
@@ -2760,7 +2757,7 @@
         <v>117</v>
       </c>
       <c r="I61" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
@@ -2792,7 +2789,7 @@
         <v>117</v>
       </c>
       <c r="I62" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
@@ -2824,7 +2821,7 @@
         <v>119</v>
       </c>
       <c r="I63" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
@@ -2856,7 +2853,7 @@
         <v>119</v>
       </c>
       <c r="I64" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
@@ -2888,7 +2885,7 @@
         <v>119</v>
       </c>
       <c r="I65" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">

--- a/data/16S/metadata_16S.xlsx
+++ b/data/16S/metadata_16S.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\Documents\GitHub\Augmentum_eDNA_metabarcoding\data\16S\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{303B24F4-F08B-4F6E-9779-C605CC0F06A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{910CB5C4-42CE-4172-B5A4-A290C3D86ED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A98CF8EC-D2DA-4B38-910A-EF3A2677D223}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="128">
   <si>
     <t>01_St1_D1</t>
   </si>
@@ -427,6 +427,21 @@
   </si>
   <si>
     <t>Tunulliarfik</t>
+  </si>
+  <si>
+    <t>MW</t>
+  </si>
+  <si>
+    <t>AW</t>
+  </si>
+  <si>
+    <t>WGSW</t>
+  </si>
+  <si>
+    <t>WGIW</t>
+  </si>
+  <si>
+    <t>Water_mass</t>
   </si>
 </sst>
 </file>
@@ -805,7 +820,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="9" max="9" width="17.88671875" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
@@ -836,6 +851,9 @@
       <c r="I1" t="s">
         <v>72</v>
       </c>
+      <c r="J1" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -868,6 +886,9 @@
       <c r="I2" t="s">
         <v>120</v>
       </c>
+      <c r="J2" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
@@ -900,6 +921,9 @@
       <c r="I3" t="s">
         <v>120</v>
       </c>
+      <c r="J3" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -932,6 +956,9 @@
       <c r="I4" t="s">
         <v>120</v>
       </c>
+      <c r="J4" t="s">
+        <v>124</v>
+      </c>
       <c r="O4" s="2"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
@@ -965,6 +992,9 @@
       <c r="I5" t="s">
         <v>120</v>
       </c>
+      <c r="J5" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -997,6 +1027,9 @@
       <c r="I6" t="s">
         <v>120</v>
       </c>
+      <c r="J6" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -1029,6 +1062,9 @@
       <c r="I7" t="s">
         <v>120</v>
       </c>
+      <c r="J7" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -1061,6 +1097,9 @@
       <c r="I8" t="s">
         <v>120</v>
       </c>
+      <c r="J8" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -1093,6 +1132,9 @@
       <c r="I9" t="s">
         <v>120</v>
       </c>
+      <c r="J9" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -1125,6 +1167,9 @@
       <c r="I10" t="s">
         <v>120</v>
       </c>
+      <c r="J10" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
@@ -1157,6 +1202,9 @@
       <c r="I11" t="s">
         <v>120</v>
       </c>
+      <c r="J11" t="s">
+        <v>123</v>
+      </c>
       <c r="O11" s="2"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
@@ -1190,6 +1238,9 @@
       <c r="I12" t="s">
         <v>120</v>
       </c>
+      <c r="J12" t="s">
+        <v>123</v>
+      </c>
       <c r="O12" s="2"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
@@ -1223,6 +1274,9 @@
       <c r="I13" t="s">
         <v>120</v>
       </c>
+      <c r="J13" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -1255,6 +1309,9 @@
       <c r="I14" t="s">
         <v>120</v>
       </c>
+      <c r="J14" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
@@ -1287,6 +1344,9 @@
       <c r="I15" t="s">
         <v>120</v>
       </c>
+      <c r="J15" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
@@ -1319,8 +1379,11 @@
       <c r="I16" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J16" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -1351,8 +1414,11 @@
       <c r="I17" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J17" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -1383,8 +1449,11 @@
       <c r="I18" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J18" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -1415,8 +1484,11 @@
       <c r="I19" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J19" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -1447,8 +1519,11 @@
       <c r="I20" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J20" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -1479,8 +1554,11 @@
       <c r="I21" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J21" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -1511,8 +1589,11 @@
       <c r="I22" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J22" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -1543,8 +1624,11 @@
       <c r="I23" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J23" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -1575,8 +1659,11 @@
       <c r="I24" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J24" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -1607,8 +1694,11 @@
       <c r="I25" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J25" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -1639,8 +1729,11 @@
       <c r="I26" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J26" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -1671,8 +1764,11 @@
       <c r="I27" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J27" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -1703,8 +1799,11 @@
       <c r="I28" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J28" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -1735,8 +1834,11 @@
       <c r="I29" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J29" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -1767,8 +1869,11 @@
       <c r="I30" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J30" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -1799,8 +1904,11 @@
       <c r="I31" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J31" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>30</v>
       </c>
@@ -1831,8 +1939,11 @@
       <c r="I32" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J32" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>31</v>
       </c>
@@ -1863,8 +1974,11 @@
       <c r="I33" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J33" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -1895,8 +2009,11 @@
       <c r="I34" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J34" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>33</v>
       </c>
@@ -1927,8 +2044,11 @@
       <c r="I35" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J35" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>34</v>
       </c>
@@ -1959,8 +2079,11 @@
       <c r="I36" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J36" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>35</v>
       </c>
@@ -1991,8 +2114,11 @@
       <c r="I37" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J37" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>36</v>
       </c>
@@ -2023,8 +2149,11 @@
       <c r="I38" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J38" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -2055,8 +2184,11 @@
       <c r="I39" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J39" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>38</v>
       </c>
@@ -2087,8 +2219,11 @@
       <c r="I40" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J40" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -2119,8 +2254,11 @@
       <c r="I41" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J41" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>40</v>
       </c>
@@ -2151,8 +2289,11 @@
       <c r="I42" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J42" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>41</v>
       </c>
@@ -2183,8 +2324,11 @@
       <c r="I43" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J43" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>42</v>
       </c>
@@ -2215,8 +2359,11 @@
       <c r="I44" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J44" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>43</v>
       </c>
@@ -2247,8 +2394,11 @@
       <c r="I45" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J45" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>44</v>
       </c>
@@ -2279,8 +2429,11 @@
       <c r="I46" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J46" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>45</v>
       </c>
@@ -2311,8 +2464,11 @@
       <c r="I47" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J47" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>46</v>
       </c>
@@ -2343,8 +2499,11 @@
       <c r="I48" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J48" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>47</v>
       </c>
@@ -2375,8 +2534,11 @@
       <c r="I49" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J49" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>48</v>
       </c>
@@ -2407,8 +2569,11 @@
       <c r="I50" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J50" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>49</v>
       </c>
@@ -2439,8 +2604,11 @@
       <c r="I51" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J51" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>50</v>
       </c>
@@ -2471,8 +2639,11 @@
       <c r="I52" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J52" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>51</v>
       </c>
@@ -2503,8 +2674,11 @@
       <c r="I53" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J53" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>52</v>
       </c>
@@ -2535,8 +2709,11 @@
       <c r="I54" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J54" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>53</v>
       </c>
@@ -2567,8 +2744,11 @@
       <c r="I55" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J55" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>54</v>
       </c>
@@ -2599,8 +2779,11 @@
       <c r="I56" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J56" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>55</v>
       </c>
@@ -2631,8 +2814,11 @@
       <c r="I57" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J57" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>56</v>
       </c>
@@ -2663,8 +2849,11 @@
       <c r="I58" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J58" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>57</v>
       </c>
@@ -2695,8 +2884,11 @@
       <c r="I59" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J59" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>58</v>
       </c>
@@ -2727,8 +2919,11 @@
       <c r="I60" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J60" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>59</v>
       </c>
@@ -2759,8 +2954,11 @@
       <c r="I61" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J61" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>60</v>
       </c>
@@ -2791,8 +2989,11 @@
       <c r="I62" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J62" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>61</v>
       </c>
@@ -2823,8 +3024,11 @@
       <c r="I63" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J63" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>62</v>
       </c>
@@ -2855,8 +3059,11 @@
       <c r="I64" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J64" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>63</v>
       </c>
@@ -2887,8 +3094,11 @@
       <c r="I65" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J65" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>64</v>
       </c>
@@ -2917,8 +3127,11 @@
       <c r="I66" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J66" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>65</v>
       </c>
@@ -2945,6 +3158,9 @@
         <v>74</v>
       </c>
       <c r="I67" t="s">
+        <v>74</v>
+      </c>
+      <c r="J67" t="s">
         <v>74</v>
       </c>
     </row>
